--- a/output/pdf_financials_xlsx/BIGG.xlsx
+++ b/output/pdf_financials_xlsx/BIGG.xlsx
@@ -669,19 +669,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.105735</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.195463</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.210674</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.446001</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.332112</v>
       </c>
     </row>
     <row r="13">
@@ -1021,19 +1021,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-6.890768</v>
+        <v>-6.996503</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-44.153182</v>
+        <v>-44.348645</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-11.202275</v>
+        <v>-11.412949</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-25.802369</v>
+        <v>-26.24837</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.252305</v>
+        <v>-1.584417</v>
       </c>
     </row>
     <row r="28">
@@ -1065,19 +1065,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-6.346665</v>
+        <v>-6.4524</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-43.771316</v>
+        <v>-43.966779</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-10.888417</v>
+        <v>-11.099091</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-25.433879</v>
+        <v>-25.87988</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.9429959999999999</v>
+        <v>-1.275108</v>
       </c>
     </row>
     <row r="30">
@@ -1087,19 +1087,19 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-44.96350622490861</v>
+        <v>-45.71259512918994</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-585.740269402983</v>
+        <v>-588.3559218608236</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-167.6508850220418</v>
+        <v>-170.8946699130075</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-204.6052818404105</v>
+        <v>-208.1931797110462</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-7.332238184141351</v>
+        <v>-9.914565455743302</v>
       </c>
     </row>
     <row r="31">
@@ -1160,7 +1160,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>31.846032</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>5.678236</v>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>31.846032</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>5.678236</v>
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>132.098545</v>
+        <v>100.252513</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>45.998941</v>
@@ -3145,19 +3145,19 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.024981</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.03038</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.030863</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.016572</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.023034</v>
       </c>
     </row>
     <row r="125">
@@ -3167,19 +3167,19 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.024981</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.03038</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.030863</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.016572</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.023034</v>
       </c>
     </row>
     <row r="126">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
@@ -7534,7 +7534,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E107" s="5" t="n">
         <v>-0.024981</v>
       </c>
@@ -10180,7 +10184,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -11222,7 +11226,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -12895,7 +12899,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E242" s="5" t="n">

--- a/output/pdf_financials_xlsx/BIGG.xlsx
+++ b/output/pdf_financials_xlsx/BIGG.xlsx
@@ -559,19 +559,19 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1.68522</v>
+        <v>1.799944</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>3.052657</v>
+        <v>3.164362</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3.47981</v>
+        <v>3.606154</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>4.568708</v>
+        <v>4.685512</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>4.100622</v>
+        <v>4.210556</v>
       </c>
     </row>
     <row r="8">
@@ -625,19 +625,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>10.346371</v>
+        <v>10.461095</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>11.280992</v>
+        <v>11.392697</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>6.702468</v>
+        <v>6.828812</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>8.53575</v>
+        <v>8.652554</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>8.023576</v>
+        <v>8.133509999999999</v>
       </c>
     </row>
     <row r="11">
@@ -647,19 +647,19 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>3.768776</v>
+        <v>3.654052</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-4.172701</v>
+        <v>-4.284406</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.470124</v>
+        <v>-0.596468</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>3.336804</v>
+        <v>3.22</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>4.534531</v>
+        <v>4.424597</v>
       </c>
     </row>
     <row r="12">
@@ -785,7 +785,7 @@
         <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.135296</v>
+        <v>-0.135296</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0.027302</v>
@@ -1896,19 +1896,19 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.663278</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.989522</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>1.579188</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>1.319238</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>1.451034</v>
       </c>
     </row>
     <row r="68">
@@ -2859,19 +2859,19 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.260996</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.430772</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.060855</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.123071</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.026702</v>
       </c>
     </row>
     <row r="112">
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.778857</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.33123</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>0</v>
@@ -2959,7 +2959,7 @@
         <v>0</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.210594</v>
       </c>
     </row>
     <row r="116">
@@ -2969,7 +2969,7 @@
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>0</v>
+        <v>-0.181464</v>
       </c>
       <c r="C116" s="3" t="n">
         <v>0</v>
@@ -2978,7 +2978,7 @@
         <v>0</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-0.004171</v>
       </c>
       <c r="F116" s="3" t="n">
         <v>0</v>
@@ -3375,19 +3375,19 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.260996</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.430772</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.060855</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.123071</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.026702</v>
       </c>
     </row>
     <row r="135">
@@ -3397,19 +3397,19 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-22.617439</v>
+        <v>-22.878435</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-18.413047</v>
+        <v>-18.843819</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-10.121447</v>
+        <v>-10.182302</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-12.387454</v>
+        <v>-12.510525</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-9.029388000000001</v>
+        <v>-9.056089999999999</v>
       </c>
     </row>
   </sheetData>
@@ -7119,7 +7119,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E96" s="5" t="n">
         <v>-0.260996</v>
       </c>
@@ -7193,7 +7197,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -7380,7 +7388,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E103" s="5" t="n">
         <v>0.778857</v>
       </c>
@@ -8644,7 +8656,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -8808,7 +8824,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -9212,7 +9232,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>PurchaseOfIntangibles</t>
+          <t>NetIntangiblesPurchaseAndSale</t>
         </is>
       </c>
       <c r="E149" s="5" t="n">
@@ -9822,7 +9842,11 @@
           <t>Director’s fees 16</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E165" s="5" t="n">
         <v>0.114724</v>
       </c>
@@ -11107,7 +11131,11 @@
           <t>Director’s fees 15</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -12091,7 +12119,11 @@
           <t>Director’s fees 17</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
@@ -12567,7 +12599,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
